--- a/livrables/decomposition_gains.xlsx
+++ b/livrables/decomposition_gains.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="decomposition_gains" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'decomposition_gains'!$A$1:$E$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'decomposition_gains'!$A$1:$E$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -980,8 +980,28 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Montréal-Ottawa</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>info_doublement_fourchette</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>part doublement/cohabitation indiscernable : 0 sur les horaires courants, jusqu'à ~12 points de marge sur GTFS 2023 (simple-VIA 48,7 vs double-CN 36,3), bornée par la marge actuelle du tronçon</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E25"/>
+  <autoFilter ref="A1:E26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/livrables/decomposition_gains.xlsx
+++ b/livrables/decomposition_gains.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="decomposition_gains" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'decomposition_gains'!$A$1:$E$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'decomposition_gains'!$A$1:$E$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,11 +427,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="46" customWidth="1" min="5" max="5"/>
@@ -472,15 +472,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>temps_recommande_avec_marge</t>
+          <t>temps_scenario_3_avec_marge</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>426.7</v>
+        <v>392.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>tbase_par_bande.csv</t>
+          <t>temps_scenario_3.csv</t>
         </is>
       </c>
     </row>
@@ -496,14 +496,14 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.1</v>
+        <v>15.7</v>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>11.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>tbase_par_bande.csv</t>
+          <t>temps_scenario_1.csv</t>
         </is>
       </c>
     </row>
@@ -519,14 +519,14 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>19.4</v>
+        <v>35.4</v>
       </c>
       <c r="D4" t="n">
-        <v>18.7</v>
+        <v>25.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>tbase_par_bande.csv</t>
+          <t>temps_scenario_1.csv</t>
         </is>
       </c>
     </row>
@@ -538,18 +538,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>gain_doublement</t>
+          <t>gain_zones_urbaines</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24.1</v>
+        <v>42.4</v>
       </c>
       <c r="D5" t="n">
-        <v>23.3</v>
+        <v>30.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>marges_2x2_synthese.csv + marges_par_intergare.csv</t>
+          <t>temps_scenario_2.csv (C1 − C2)</t>
         </is>
       </c>
     </row>
@@ -561,18 +561,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>gain_cohabitation</t>
+          <t>gain_courbes_au_doublement</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>40.2</v>
+        <v>14.2</v>
       </c>
       <c r="D6" t="n">
-        <v>38.7</v>
+        <v>10.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>résidu (G − autres parts)</t>
+          <t>temps_scenario_3.csv (C2 − C3)</t>
         </is>
       </c>
     </row>
@@ -584,15 +584,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>controle_horaire_actuel_H</t>
+          <t>gain_doublement</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>530.5</v>
+        <v>22.1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>16.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>tbase_par_bande.csv (médiane GTFS)</t>
+          <t>marges_2x2_synthese.csv + marges_par_intergare.csv</t>
         </is>
       </c>
     </row>
@@ -604,15 +607,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>controle_gain_total_G</t>
+          <t>gain_cohabitation</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>103.8</v>
+        <v>7.9</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>H − C ; somme des quatre parts = G par construction</t>
+          <t>résidu (H − C1 − autres parts)</t>
         </is>
       </c>
     </row>
@@ -624,58 +630,55 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>controle_ecart_ordres_shapley</t>
+          <t>controle_horaire_actuel_H</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5.7</v>
+        <v>530.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>écart |plafond d'abord − pendulaire d'abord|</t>
+          <t>temps_scenario_1.csv (médiane GTFS)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Québec-Montréal</t>
+          <t>Québec-Toronto (via Montréal)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>temps_recommande_avec_marge</t>
+          <t>controle_gain_total_G</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>149.6</v>
+        <v>137.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>tbase_par_bande.csv</t>
+          <t>H − C3 ; somme des parts = G par construction</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Québec-Montréal</t>
+          <t>Québec-Toronto (via Montréal)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>gain_releve_plafond</t>
+          <t>controle_ecart_ordres_shapley</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="D11" t="n">
-        <v>9.699999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>tbase_par_bande.csv</t>
+          <t>écart |plafond d'abord − pendulaire d'abord|</t>
         </is>
       </c>
     </row>
@@ -687,18 +690,15 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>gain_pendulaire</t>
+          <t>temps_scenario_3_avec_marge</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="D12" t="n">
-        <v>20.3</v>
+        <v>125.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>tbase_par_bande.csv</t>
+          <t>temps_scenario_3.csv</t>
         </is>
       </c>
     </row>
@@ -710,18 +710,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>gain_doublement</t>
+          <t>gain_releve_plafond</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>24.1</v>
+        <v>3.9</v>
       </c>
       <c r="D13" t="n">
-        <v>45.6</v>
+        <v>5</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>marges_2x2_synthese.csv + marges_par_intergare.csv</t>
+          <t>temps_scenario_1.csv</t>
         </is>
       </c>
     </row>
@@ -733,18 +733,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>gain_cohabitation</t>
+          <t>gain_pendulaire</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12.9</v>
+        <v>15.5</v>
       </c>
       <c r="D14" t="n">
-        <v>24.4</v>
+        <v>20.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>résidu (G − autres parts)</t>
+          <t>temps_scenario_1.csv</t>
         </is>
       </c>
     </row>
@@ -756,15 +756,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>controle_horaire_actuel_H</t>
+          <t>gain_zones_urbaines</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>202.5</v>
+        <v>19.6</v>
+      </c>
+      <c r="D15" t="n">
+        <v>25.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>tbase_par_bande.csv (médiane GTFS)</t>
+          <t>temps_scenario_2.csv (C1 − C2)</t>
         </is>
       </c>
     </row>
@@ -776,15 +779,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>controle_gain_total_G</t>
+          <t>gain_courbes_au_doublement</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>52.9</v>
+        <v>14.2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>18.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>H − C ; somme des quatre parts = G par construction</t>
+          <t>temps_scenario_3.csv (C2 − C3)</t>
         </is>
       </c>
     </row>
@@ -796,104 +802,101 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>controle_ecart_ordres_shapley</t>
+          <t>gain_doublement</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2.1</v>
+        <v>22.1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>28.8</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>écart |plafond d'abord − pendulaire d'abord|</t>
+          <t>marges_2x2_synthese.csv + marges_par_intergare.csv</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Montréal-Ottawa</t>
+          <t>Québec-Montréal</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>temps_recommande_avec_marge</t>
+          <t>gain_cohabitation</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>105.8</v>
+        <v>1.5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>tbase_par_bande.csv</t>
+          <t>résidu (H − C1 − autres parts)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Montréal-Ottawa</t>
+          <t>Québec-Montréal</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gain_releve_plafond</t>
+          <t>controle_horaire_actuel_H</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" t="n">
-        <v>12.4</v>
+        <v>202.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>tbase_par_bande.csv</t>
+          <t>temps_scenario_1.csv (médiane GTFS)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Montréal-Ottawa</t>
+          <t>Québec-Montréal</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gain_pendulaire</t>
+          <t>controle_gain_total_G</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="D20" t="n">
-        <v>67.2</v>
+        <v>76.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>tbase_par_bande.csv</t>
+          <t>H − C3 ; somme des parts = G par construction</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Montréal-Ottawa</t>
+          <t>Québec-Montréal</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gain_doublement</t>
+          <t>controle_ecart_ordres_shapley</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>marges_2x2_synthese.csv + marges_par_intergare.csv</t>
+          <t>écart |plafond d'abord − pendulaire d'abord|</t>
         </is>
       </c>
     </row>
@@ -905,18 +908,15 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>gain_cohabitation</t>
+          <t>temps_scenario_3_avec_marge</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D22" t="n">
-        <v>20.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>résidu (G − autres parts)</t>
+          <t>temps_scenario_3.csv</t>
         </is>
       </c>
     </row>
@@ -928,15 +928,18 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>controle_horaire_actuel_H</t>
+          <t>gain_releve_plafond</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>122</v>
+        <v>1.2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3.7</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>tbase_par_bande.csv (médiane GTFS)</t>
+          <t>temps_scenario_1.csv</t>
         </is>
       </c>
     </row>
@@ -948,15 +951,18 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>controle_gain_total_G</t>
+          <t>gain_pendulaire</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>16.2</v>
+        <v>9.4</v>
+      </c>
+      <c r="D24" t="n">
+        <v>28.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>H − C ; somme des quatre parts = G par construction</t>
+          <t>temps_scenario_1.csv</t>
         </is>
       </c>
     </row>
@@ -968,15 +974,18 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>controle_ecart_ordres_shapley</t>
+          <t>gain_zones_urbaines</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.7</v>
+        <v>15.6</v>
+      </c>
+      <c r="D25" t="n">
+        <v>46.7</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>écart |plafond d'abord − pendulaire d'abord|</t>
+          <t>temps_scenario_2.csv (C1 − C2)</t>
         </is>
       </c>
     </row>
@@ -988,20 +997,149 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>info_doublement_fourchette</t>
+          <t>gain_courbes_au_doublement</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3.3</v>
+        <v>7.1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>21.4</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>part doublement/cohabitation indiscernable : 0 sur les horaires courants, jusqu'à ~12 points de marge sur GTFS 2023 (simple-VIA 48,7 vs double-CN 36,3), bornée par la marge actuelle du tronçon</t>
+          <t>temps_scenario_3.csv (C2 − C3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Montréal-Ottawa</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>gain_doublement</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>marges_2x2_synthese.csv + marges_par_intergare.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Montréal-Ottawa</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>gain_cohabitation</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>résidu (H − C1 − autres parts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Montréal-Ottawa</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>controle_horaire_actuel_H</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>122</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>temps_scenario_1.csv (médiane GTFS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Montréal-Ottawa</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>controle_gain_total_G</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>H − C3 ; somme des parts = G par construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Montréal-Ottawa</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>controle_ecart_ordres_shapley</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>écart |plafond d'abord − pendulaire d'abord|</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Montréal-Ottawa</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>info_marge_normative_excedentaire</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>l'horaire actuel porte moins de 10 % de marge : la marge normative absorbe cette part du gain pendulaire (attribution plafond+pendulaire réduite d'autant)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E26"/>
+  <autoFilter ref="A1:E32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/livrables/decomposition_gains.xlsx
+++ b/livrables/decomposition_gains.xlsx
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>392.8</v>
+        <v>370</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -496,10 +496,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15.7</v>
+        <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>11.4</v>
+        <v>18.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -519,10 +519,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>35.4</v>
+        <v>38.2</v>
       </c>
       <c r="D4" t="n">
-        <v>25.7</v>
+        <v>23.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>42.4</v>
+        <v>42.6</v>
       </c>
       <c r="D5" t="n">
-        <v>30.8</v>
+        <v>26.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -565,10 +565,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>14.2</v>
+        <v>19.7</v>
       </c>
       <c r="D6" t="n">
-        <v>10.3</v>
+        <v>12.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         <v>22.1</v>
       </c>
       <c r="D7" t="n">
-        <v>16.1</v>
+        <v>13.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         <v>7.9</v>
       </c>
       <c r="D8" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>137.7</v>
+        <v>160.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>125.7</v>
+        <v>116.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3.9</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>8.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -737,10 +737,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="D14" t="n">
-        <v>20.2</v>
+        <v>19.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>19.6</v>
       </c>
       <c r="D15" t="n">
-        <v>25.5</v>
+        <v>22.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -783,10 +783,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>14.2</v>
+        <v>19.7</v>
       </c>
       <c r="D16" t="n">
-        <v>18.5</v>
+        <v>22.8</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>22.1</v>
       </c>
       <c r="D17" t="n">
-        <v>28.8</v>
+        <v>25.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>1.5</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>76.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>88.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="D23" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>9.4</v>
+        <v>9.9</v>
       </c>
       <c r="D24" t="n">
-        <v>28.2</v>
+        <v>25.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -978,10 +978,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="D25" t="n">
-        <v>46.7</v>
+        <v>39.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>7.1</v>
+        <v>11.3</v>
       </c>
       <c r="D26" t="n">
-        <v>21.4</v>
+        <v>28.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>33.4</v>
+        <v>39.4</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>

--- a/livrables/decomposition_gains.xlsx
+++ b/livrables/decomposition_gains.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="decomposition_gains" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'decomposition_gains'!$A$1:$E$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'decomposition_gains'!$A$1:$E$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,11 +427,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="46" customWidth="1" min="5" max="5"/>
@@ -472,15 +472,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>temps_scenario_3_avec_marge</t>
+          <t>temps_scenario_2_avec_marge</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>370</v>
+        <v>389.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>temps_scenario_3.csv</t>
+          <t>temps_scenario_2.csv (pendulaire, 201) × 1,10</t>
         </is>
       </c>
     </row>
@@ -492,18 +492,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>gain_releve_plafond</t>
+          <t>gain_cohabitation</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>57.5</v>
       </c>
       <c r="D3" t="n">
-        <v>18.7</v>
+        <v>40.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>temps_scenario_1.csv</t>
+          <t>G − les trois autres postes : mou de l'horaire au-delà de 10 %, interurbain et zones urbaines ; doublement et régime réunis</t>
         </is>
       </c>
     </row>
@@ -519,14 +519,14 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>38.2</v>
+        <v>29.3</v>
       </c>
       <c r="D4" t="n">
-        <v>23.8</v>
+        <v>20.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>temps_scenario_1.csv</t>
+          <t>temps_scenario_1.csv (base − pendulaire, 153) × 1,10</t>
         </is>
       </c>
     </row>
@@ -542,14 +542,14 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>42.6</v>
+        <v>8.5</v>
       </c>
       <c r="D5" t="n">
-        <v>26.5</v>
+        <v>6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>temps_scenario_2.csv (C1 − C2)</t>
+          <t>gains_urbains.csv : courbes (pendulaire) + signalisation des blocs urbains, sans le mou de cohabitation</t>
         </is>
       </c>
     </row>
@@ -561,18 +561,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>gain_courbes_au_doublement</t>
+          <t>gain_changement_classe</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19.7</v>
+        <v>45.5</v>
       </c>
       <c r="D6" t="n">
-        <v>12.3</v>
+        <v>32.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>temps_scenario_3.csv (C2 − C3)</t>
+          <t>temps_scenario_2.csv (pendulaire, 153 − 201) × 1,10 − signalisation urbaine : passages à niveau et signalisation, interurbain</t>
         </is>
       </c>
     </row>
@@ -584,18 +584,15 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>gain_doublement</t>
+          <t>info_cohabitation_dont_doublement</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>22.1</v>
       </c>
-      <c r="D7" t="n">
-        <v>13.8</v>
-      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>marges_2x2_synthese.csv + marges_par_intergare.csv</t>
+          <t>part de la cohabitation que le doublement rachète : (médiane simple-CN − médiane double-CN) × Σ T_base des paires simple-CN (marges_2x2_synthese.csv, marges_par_intergare.csv) ; le reste est l'objet de l'étude de circulation</t>
         </is>
       </c>
     </row>
@@ -607,18 +604,15 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>gain_cohabitation</t>
+          <t>info_cohabitation_dont_zones_urbaines</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="D8" t="n">
-        <v>4.9</v>
+        <v>33.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>résidu (H − C1 − autres parts)</t>
+          <t>mou de l'horaire actuel dans les blocs urbains (gains_urbains.csv), compté dans la cohabitation et non dans les zones urbaines</t>
         </is>
       </c>
     </row>
@@ -654,31 +648,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>160.5</v>
+        <v>140.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>H − C3 ; somme des parts = G par construction</t>
+          <t>H − C ; somme des quatre parts = G par construction</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Québec-Toronto (via Montréal)</t>
+          <t>Québec-Montréal</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>controle_ecart_ordres_shapley</t>
+          <t>temps_scenario_2_avec_marge</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9.800000000000001</v>
+        <v>135.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>écart |plafond d'abord − pendulaire d'abord|</t>
+          <t>temps_scenario_2.csv (pendulaire, 201) × 1,10</t>
         </is>
       </c>
     </row>
@@ -690,15 +684,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>temps_scenario_3_avec_marge</t>
+          <t>gain_cohabitation</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>116.1</v>
+        <v>37.7</v>
+      </c>
+      <c r="D12" t="n">
+        <v>56.5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>temps_scenario_3.csv</t>
+          <t>G − les trois autres postes : mou de l'horaire au-delà de 10 %, interurbain et zones urbaines ; doublement et régime réunis</t>
         </is>
       </c>
     </row>
@@ -710,18 +707,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>gain_releve_plafond</t>
+          <t>gain_pendulaire</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>12.8</v>
       </c>
       <c r="D13" t="n">
-        <v>8.1</v>
+        <v>19.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>temps_scenario_1.csv</t>
+          <t>temps_scenario_1.csv (base − pendulaire, 153) × 1,10</t>
         </is>
       </c>
     </row>
@@ -733,18 +730,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>gain_pendulaire</t>
+          <t>gain_zones_urbaines</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.5</v>
+        <v>4.5</v>
       </c>
       <c r="D14" t="n">
-        <v>19.1</v>
+        <v>6.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>temps_scenario_1.csv</t>
+          <t>gains_urbains.csv : courbes (pendulaire) + signalisation des blocs urbains, sans le mou de cohabitation</t>
         </is>
       </c>
     </row>
@@ -756,18 +753,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>gain_zones_urbaines</t>
+          <t>gain_changement_classe</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>19.6</v>
+        <v>11.8</v>
       </c>
       <c r="D15" t="n">
-        <v>22.6</v>
+        <v>17.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>temps_scenario_2.csv (C1 − C2)</t>
+          <t>temps_scenario_2.csv (pendulaire, 153 − 201) × 1,10 − signalisation urbaine : passages à niveau et signalisation, interurbain</t>
         </is>
       </c>
     </row>
@@ -779,18 +776,15 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>gain_courbes_au_doublement</t>
+          <t>info_cohabitation_dont_doublement</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="D16" t="n">
-        <v>22.8</v>
+        <v>22.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>temps_scenario_3.csv (C2 − C3)</t>
+          <t>part de la cohabitation que le doublement rachète : (médiane simple-CN − médiane double-CN) × Σ T_base des paires simple-CN (marges_2x2_synthese.csv, marges_par_intergare.csv) ; le reste est l'objet de l'étude de circulation</t>
         </is>
       </c>
     </row>
@@ -802,18 +796,15 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>gain_doublement</t>
+          <t>info_cohabitation_dont_zones_urbaines</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="D17" t="n">
-        <v>25.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>marges_2x2_synthese.csv + marges_par_intergare.csv</t>
+          <t>mou de l'horaire actuel dans les blocs urbains (gains_urbains.csv), compté dans la cohabitation et non dans les zones urbaines</t>
         </is>
       </c>
     </row>
@@ -825,18 +816,15 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>gain_cohabitation</t>
+          <t>controle_horaire_actuel_H</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1.8</v>
+        <v>202.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>résidu (H − C1 − autres parts)</t>
+          <t>temps_scenario_1.csv (médiane GTFS)</t>
         </is>
       </c>
     </row>
@@ -848,213 +836,207 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>controle_horaire_actuel_H</t>
+          <t>controle_gain_total_G</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>202.5</v>
+        <v>66.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>temps_scenario_1.csv (médiane GTFS)</t>
+          <t>H − C ; somme des quatre parts = G par construction</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Québec-Montréal</t>
+          <t>Montréal-Toronto</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>controle_gain_total_G</t>
+          <t>temps_scenario_2_avec_marge</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>86.40000000000001</v>
+        <v>244</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>H − C3 ; somme des parts = G par construction</t>
+          <t>temps_scenario_2.csv (pendulaire, 201) × 1,10</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Québec-Montréal</t>
+          <t>Montréal-Toronto</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>controle_ecart_ordres_shapley</t>
+          <t>gain_cohabitation</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3.4</v>
+        <v>19.8</v>
+      </c>
+      <c r="D21" t="n">
+        <v>26.7</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>écart |plafond d'abord − pendulaire d'abord|</t>
+          <t>G − les trois autres postes : mou de l'horaire au-delà de 10 %, interurbain et zones urbaines ; doublement et régime réunis</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Montréal-Ottawa</t>
+          <t>Montréal-Toronto</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>temps_scenario_3_avec_marge</t>
+          <t>gain_pendulaire</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>82.59999999999999</v>
+        <v>16.5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>22.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>temps_scenario_3.csv</t>
+          <t>temps_scenario_1.csv (base − pendulaire, 153) × 1,10</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Montréal-Ottawa</t>
+          <t>Montréal-Toronto</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>gain_releve_plafond</t>
+          <t>gain_zones_urbaines</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>temps_scenario_1.csv</t>
+          <t>gains_urbains.csv : courbes (pendulaire) + signalisation des blocs urbains, sans le mou de cohabitation</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Montréal-Ottawa</t>
+          <t>Montréal-Toronto</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gain_pendulaire</t>
+          <t>gain_changement_classe</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>9.9</v>
+        <v>33.8</v>
       </c>
       <c r="D24" t="n">
-        <v>25.3</v>
+        <v>45.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>temps_scenario_1.csv</t>
+          <t>temps_scenario_2.csv (pendulaire, 153 − 201) × 1,10 − signalisation urbaine : passages à niveau et signalisation, interurbain</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Montréal-Ottawa</t>
+          <t>Montréal-Toronto</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gain_zones_urbaines</t>
+          <t>info_cohabitation_dont_doublement</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="D25" t="n">
-        <v>39.9</v>
+        <v>0</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>temps_scenario_2.csv (C1 − C2)</t>
+          <t>part de la cohabitation que le doublement rachète : (médiane simple-CN − médiane double-CN) × Σ T_base des paires simple-CN (marges_2x2_synthese.csv, marges_par_intergare.csv) ; le reste est l'objet de l'étude de circulation</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Montréal-Ottawa</t>
+          <t>Montréal-Toronto</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>gain_courbes_au_doublement</t>
+          <t>info_cohabitation_dont_zones_urbaines</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="D26" t="n">
-        <v>28.8</v>
+        <v>18.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>temps_scenario_3.csv (C2 − C3)</t>
+          <t>mou de l'horaire actuel dans les blocs urbains (gains_urbains.csv), compté dans la cohabitation et non dans les zones urbaines</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Montréal-Ottawa</t>
+          <t>Montréal-Toronto</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>gain_doublement</t>
+          <t>controle_horaire_actuel_H</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0</v>
+        <v>318</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>marges_2x2_synthese.csv + marges_par_intergare.csv</t>
+          <t>temps_scenario_1.csv (médiane GTFS)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Montréal-Ottawa</t>
+          <t>Montréal-Toronto</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>gain_cohabitation</t>
+          <t>controle_gain_total_G</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>résidu (H − C1 − autres parts)</t>
+          <t>H − C ; somme des quatre parts = G par construction</t>
         </is>
       </c>
     </row>
@@ -1066,15 +1048,15 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>controle_horaire_actuel_H</t>
+          <t>temps_scenario_2_avec_marge</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>122</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>temps_scenario_1.csv (médiane GTFS)</t>
+          <t>temps_scenario_2.csv (pendulaire, 201) × 1,10</t>
         </is>
       </c>
     </row>
@@ -1086,15 +1068,18 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>controle_gain_total_G</t>
+          <t>gain_cohabitation</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>39.4</v>
+        <v>9.5</v>
+      </c>
+      <c r="D30" t="n">
+        <v>33.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>H − C3 ; somme des parts = G par construction</t>
+          <t>G − les trois autres postes : mou de l'horaire au-delà de 10 %, interurbain et zones urbaines ; doublement et régime réunis</t>
         </is>
       </c>
     </row>
@@ -1106,15 +1091,18 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>controle_ecart_ordres_shapley</t>
+          <t>gain_pendulaire</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="D31" t="n">
+        <v>39.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>écart |plafond d'abord − pendulaire d'abord|</t>
+          <t>temps_scenario_1.csv (base − pendulaire, 153) × 1,10</t>
         </is>
       </c>
     </row>
@@ -1126,20 +1114,126 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>info_marge_normative_excedentaire</t>
+          <t>gain_zones_urbaines</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
+      </c>
+      <c r="D32" t="n">
+        <v>6.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>l'horaire actuel porte moins de 10 % de marge : la marge normative absorbe cette part du gain pendulaire (attribution plafond+pendulaire réduite d'autant)</t>
+          <t>gains_urbains.csv : courbes (pendulaire) + signalisation des blocs urbains, sans le mou de cohabitation</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Montréal-Ottawa</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>gain_changement_classe</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="D33" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>temps_scenario_2.csv (pendulaire, 153 − 201) × 1,10 − signalisation urbaine : passages à niveau et signalisation, interurbain</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Montréal-Ottawa</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>info_cohabitation_dont_doublement</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>part de la cohabitation que le doublement rachète : (médiane simple-CN − médiane double-CN) × Σ T_base des paires simple-CN (marges_2x2_synthese.csv, marges_par_intergare.csv) ; le reste est l'objet de l'étude de circulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Montréal-Ottawa</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>info_cohabitation_dont_zones_urbaines</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>mou de l'horaire actuel dans les blocs urbains (gains_urbains.csv), compté dans la cohabitation et non dans les zones urbaines</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Montréal-Ottawa</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>controle_horaire_actuel_H</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>122</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>temps_scenario_1.csv (médiane GTFS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Montréal-Ottawa</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>controle_gain_total_G</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>H − C ; somme des quatre parts = G par construction</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E32"/>
+  <autoFilter ref="A1:E37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>